--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 Python- My Data My Code/12603513-MDMC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8412DEF-7BD0-46DE-921D-BEB2E487AF90}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53EDBD32-4E9C-4123-8576-AC1673F3E5DD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,18 @@
   </si>
   <si>
     <t>I have to give time on Python and SQL.</t>
+  </si>
+  <si>
+    <t>22-08-2026</t>
+  </si>
+  <si>
+    <t>CA is coming</t>
+  </si>
+  <si>
+    <t>23-08-2026</t>
+  </si>
+  <si>
+    <t>I have to work hard in C++</t>
   </si>
 </sst>
 </file>
@@ -516,6 +528,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1204,48 +1220,96 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>45</v>
+      </c>
+      <c r="D10" s="14">
+        <v>240</v>
+      </c>
+      <c r="E10" s="14">
+        <v>120</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>45</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>180</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53EDBD32-4E9C-4123-8576-AC1673F3E5DD}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9CC6360-430A-457F-BF4F-72D1A7FCD112}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,21 @@
   </si>
   <si>
     <t>I have to work hard in C++</t>
+  </si>
+  <si>
+    <t>24-08-2026</t>
+  </si>
+  <si>
+    <t>Try to give time to every subject</t>
+  </si>
+  <si>
+    <t>25-08-2026</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1312,48 +1327,96 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>50</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>30</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>30</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9CC6360-430A-457F-BF4F-72D1A7FCD112}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E90E12-D4DF-4E57-99AC-8E6245FD37D1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,15 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>26-08-2026</t>
+  </si>
+  <si>
+    <t>27-08-2026</t>
+  </si>
+  <si>
+    <t>Work hard+Smart work Ershad</t>
   </si>
 </sst>
 </file>
@@ -1418,49 +1427,97 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="14">
+        <v>300</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>240</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>50</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E90E12-D4DF-4E57-99AC-8E6245FD37D1}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D62151DC-B9A1-4046-88D0-EEF552419CA2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>Work hard+Smart work Ershad</t>
+  </si>
+  <si>
+    <t>28-08-2026</t>
+  </si>
+  <si>
+    <t>Eat less do more</t>
   </si>
 </sst>
 </file>
@@ -1520,26 +1526,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>240</v>
+      </c>
+      <c r="E16" s="14">
+        <v>70</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D62151DC-B9A1-4046-88D0-EEF552419CA2}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD5B339-30A1-4C71-A9BC-E8C90D6B7BBD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,36 @@
   </si>
   <si>
     <t>Eat less do more</t>
+  </si>
+  <si>
+    <t>29-08-2026</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Consistency is the key to success.</t>
+  </si>
+  <si>
+    <t>30-08-2026</t>
+  </si>
+  <si>
+    <t>Everyday is the new opportunity to get closer to our goal.</t>
+  </si>
+  <si>
+    <t>31-08-2026</t>
+  </si>
+  <si>
+    <t>Eat less do more.</t>
+  </si>
+  <si>
+    <t>Totally exhausted</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Felling very tired.</t>
   </si>
 </sst>
 </file>
@@ -1571,115 +1601,235 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="14">
+        <v>390</v>
+      </c>
+      <c r="C17" s="14">
+        <v>42</v>
+      </c>
+      <c r="D17" s="14">
+        <v>125</v>
+      </c>
+      <c r="E17" s="14">
+        <v>68</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>90</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>715</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>725</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>38</v>
+      </c>
+      <c r="D18" s="14">
+        <v>90</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>45</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>563</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>877</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="14">
+        <v>320</v>
+      </c>
+      <c r="C19" s="14">
+        <v>48</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>46</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>794</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>646</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46031</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
+        <v>50</v>
+      </c>
+      <c r="D20" s="14">
+        <v>160</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46062</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>100</v>
+      </c>
+      <c r="E21" s="14">
+        <v>65</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>435</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
